--- a/docs/workbook-split/dateien/Bilanz.xlsx
+++ b/docs/workbook-split/dateien/Bilanz.xlsx
@@ -683,9 +683,8 @@
           <t>Summe Technische Anlagen und Maschinen</t>
         </is>
       </c>
-      <c r="F8" s="6">
-        <f>'[D Finanzen.xlsx]D Finanzen'!D636</f>
-        <v/>
+      <c r="F8" s="6" t="n">
+        <v>27268</v>
       </c>
       <c r="G8" s="1" t="n"/>
       <c r="H8" s="1" t="n"/>
@@ -695,9 +694,8 @@
         </is>
       </c>
       <c r="J8" s="1" t="n"/>
-      <c r="K8" s="7">
-        <f>SUM('[D Finanzen.xlsx]D Finanzen'!D633,'[D Finanzen.xlsx]D Finanzen'!D634,'[D Finanzen.xlsx]D Finanzen'!D635,'[D Finanzen.xlsx]D Finanzen'!D640,'[D Finanzen.xlsx]D Finanzen'!D641,'[D Finanzen.xlsx]D Finanzen'!D642,'[D Finanzen.xlsx]D Finanzen'!D643,'[D Finanzen.xlsx]D Finanzen'!D645,'[D Finanzen.xlsx]D Finanzen'!D647,'[D Finanzen.xlsx]D Finanzen'!D648,'[D Finanzen.xlsx]D Finanzen'!D649,'[D Finanzen.xlsx]D Finanzen'!D650,'[D Finanzen.xlsx]D Finanzen'!D651,'[D Finanzen.xlsx]D Finanzen'!D652,'[D Finanzen.xlsx]D Finanzen'!D653,'[D Finanzen.xlsx]D Finanzen'!D661,'[D Finanzen.xlsx]D Finanzen'!D663,'[D Finanzen.xlsx]D Finanzen'!D665,'[D Finanzen.xlsx]D Finanzen'!D670,'[D Finanzen.xlsx]D Finanzen'!D671,'[D Finanzen.xlsx]D Finanzen'!D673,'[D Finanzen.xlsx]D Finanzen'!D675,'[D Finanzen.xlsx]D Finanzen'!D676,'[D Finanzen.xlsx]D Finanzen'!D680,'[D Finanzen.xlsx]D Finanzen'!D681,'[D Finanzen.xlsx]D Finanzen'!D682,'[D Finanzen.xlsx]D Finanzen'!D687,'[D Finanzen.xlsx]D Finanzen'!D688,'[D Finanzen.xlsx]D Finanzen'!D689,'[D Finanzen.xlsx]D Finanzen'!D690,'[D Finanzen.xlsx]D Finanzen'!D691,'[D Finanzen.xlsx]D Finanzen'!D692,'[D Finanzen.xlsx]D Finanzen'!D695,'[D Finanzen.xlsx]D Finanzen'!D696,'[D Finanzen.xlsx]D Finanzen'!D697,'[D Finanzen.xlsx]D Finanzen'!D698,'[D Finanzen.xlsx]D Finanzen'!D699,'[D Finanzen.xlsx]D Finanzen'!D700,'[D Finanzen.xlsx]D Finanzen'!D701,'[D Finanzen.xlsx]D Finanzen'!D702,'[D Finanzen.xlsx]D Finanzen'!D704,'[D Finanzen.xlsx]D Finanzen'!D705,'[D Finanzen.xlsx]D Finanzen'!D711,'[D Finanzen.xlsx]D Finanzen'!D712,'[D Finanzen.xlsx]D Finanzen'!D713,'[D Finanzen.xlsx]D Finanzen'!D714,'[D Finanzen.xlsx]D Finanzen'!D719,'[D Finanzen.xlsx]D Finanzen'!D720,'[D Finanzen.xlsx]D Finanzen'!D721)</f>
-        <v/>
+      <c r="K8" s="7" t="n">
+        <v>6753194.719999998</v>
       </c>
       <c r="L8" s="1" t="n"/>
       <c r="M8" s="1" t="n"/>
@@ -720,9 +718,8 @@
           <t>Summe Andere Anlagen, Betriebs- und</t>
         </is>
       </c>
-      <c r="F9" s="6">
-        <f>'[D Finanzen.xlsx]D Finanzen'!D654</f>
-        <v/>
+      <c r="F9" s="6" t="n">
+        <v>421370</v>
       </c>
       <c r="G9" s="1" t="n"/>
       <c r="H9" s="1" t="n"/>
@@ -750,9 +747,8 @@
           <t>Summe Sachanlagen</t>
         </is>
       </c>
-      <c r="F10" s="6">
-        <f>'[D Finanzen.xlsx]D Finanzen'!D656</f>
-        <v/>
+      <c r="F10" s="6" t="n">
+        <v>448638</v>
       </c>
       <c r="G10" s="1" t="n"/>
       <c r="H10" s="1" t="n"/>
@@ -762,9 +758,8 @@
         </is>
       </c>
       <c r="J10" s="1" t="n"/>
-      <c r="K10" s="7">
-        <f>-SUM('[D Finanzen.xlsx]D Finanzen'!D727,'[D Finanzen.xlsx]D Finanzen'!D729,'[D Finanzen.xlsx]D Finanzen'!D732,'[D Finanzen.xlsx]D Finanzen'!D733,'[D Finanzen.xlsx]D Finanzen'!D736,'[D Finanzen.xlsx]D Finanzen'!D738,'[D Finanzen.xlsx]D Finanzen'!D739,'[D Finanzen.xlsx]D Finanzen'!D740,'[D Finanzen.xlsx]D Finanzen'!D741,'[D Finanzen.xlsx]D Finanzen'!D742,'[D Finanzen.xlsx]D Finanzen'!D743,'[D Finanzen.xlsx]D Finanzen'!D745,'[D Finanzen.xlsx]D Finanzen'!D746,'[D Finanzen.xlsx]D Finanzen'!D747,'[D Finanzen.xlsx]D Finanzen'!D752,'[D Finanzen.xlsx]D Finanzen'!D753,'[D Finanzen.xlsx]D Finanzen'!D754,'[D Finanzen.xlsx]D Finanzen'!D758,'[D Finanzen.xlsx]D Finanzen'!D759,'[D Finanzen.xlsx]D Finanzen'!D761,'[D Finanzen.xlsx]D Finanzen'!D763,'[D Finanzen.xlsx]D Finanzen'!D764,'[D Finanzen.xlsx]D Finanzen'!D765,'[D Finanzen.xlsx]D Finanzen'!D770,'[D Finanzen.xlsx]D Finanzen'!D771,'[D Finanzen.xlsx]D Finanzen'!D772,'[D Finanzen.xlsx]D Finanzen'!D773,'[D Finanzen.xlsx]D Finanzen'!D774,'[D Finanzen.xlsx]D Finanzen'!D775,'[D Finanzen.xlsx]D Finanzen'!D776,'[D Finanzen.xlsx]D Finanzen'!D777,'[D Finanzen.xlsx]D Finanzen'!D778,'[D Finanzen.xlsx]D Finanzen'!D781,'[D Finanzen.xlsx]D Finanzen'!D783,'[D Finanzen.xlsx]D Finanzen'!D784,'[D Finanzen.xlsx]D Finanzen'!D785,'[D Finanzen.xlsx]D Finanzen'!D786,'[D Finanzen.xlsx]D Finanzen'!D787,'[D Finanzen.xlsx]D Finanzen'!D788,'[D Finanzen.xlsx]D Finanzen'!D793,'[D Finanzen.xlsx]D Finanzen'!D794,'[D Finanzen.xlsx]D Finanzen'!D795,'[D Finanzen.xlsx]D Finanzen'!D796)</f>
-        <v/>
+      <c r="K10" s="7" t="n">
+        <v>6753194.719999999</v>
       </c>
       <c r="L10" s="1" t="n"/>
       <c r="M10" s="1" t="n"/>
@@ -787,9 +782,8 @@
           <t>Summe Anlagevermoegen</t>
         </is>
       </c>
-      <c r="F11" s="9">
-        <f>'[D Finanzen.xlsx]D Finanzen'!D657</f>
-        <v/>
+      <c r="F11" s="9" t="n">
+        <v>448638</v>
       </c>
       <c r="G11" s="1" t="n"/>
       <c r="H11" s="1" t="n"/>
@@ -817,9 +811,8 @@
           <t>Summe Vorraete</t>
         </is>
       </c>
-      <c r="F12" s="6">
-        <f>'[D Finanzen.xlsx]D Finanzen'!D666</f>
-        <v/>
+      <c r="F12" s="6" t="n">
+        <v>2332501.17</v>
       </c>
       <c r="G12" s="1" t="n"/>
       <c r="H12" s="1" t="n"/>
@@ -829,9 +822,8 @@
         </is>
       </c>
       <c r="J12" s="1" t="n"/>
-      <c r="K12" s="7">
-        <f>ROUND(K8-K10,2)</f>
-        <v/>
+      <c r="K12" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="L12" s="1" t="n"/>
       <c r="M12" s="1" t="n"/>
@@ -854,9 +846,8 @@
           <t>Summe Ford. L+L</t>
         </is>
       </c>
-      <c r="F13" s="6">
-        <f>'[D Finanzen.xlsx]D Finanzen'!D677</f>
-        <v/>
+      <c r="F13" s="6" t="n">
+        <v>1659741.32</v>
       </c>
       <c r="G13" s="1" t="n"/>
       <c r="H13" s="1" t="n"/>
@@ -884,9 +875,8 @@
           <t>Summe Ford. verbund.</t>
         </is>
       </c>
-      <c r="F14" s="6">
-        <f>'[D Finanzen.xlsx]D Finanzen'!D683</f>
-        <v/>
+      <c r="F14" s="6" t="n">
+        <v>25470.03</v>
       </c>
       <c r="G14" s="1" t="n"/>
       <c r="H14" s="1" t="n"/>
@@ -914,9 +904,8 @@
           <t>Summe Sonst. VermögensG.</t>
         </is>
       </c>
-      <c r="F15" s="6">
-        <f>'[D Finanzen.xlsx]D Finanzen'!D706</f>
-        <v/>
+      <c r="F15" s="6" t="n">
+        <v>2271367.1</v>
       </c>
       <c r="G15" s="1" t="n"/>
       <c r="H15" s="1" t="n"/>
@@ -944,9 +933,8 @@
           <t>Summe Ford. / Sonst. VgG</t>
         </is>
       </c>
-      <c r="F16" s="6">
-        <f>'[D Finanzen.xlsx]D Finanzen'!D707</f>
-        <v/>
+      <c r="F16" s="6" t="n">
+        <v>3956578.45</v>
       </c>
       <c r="G16" s="1" t="n"/>
       <c r="H16" s="1" t="n"/>
@@ -974,9 +962,8 @@
           <t>Summe Schecks, Kassenbestand, Bankguthaben</t>
         </is>
       </c>
-      <c r="F17" s="6">
-        <f>'[D Finanzen.xlsx]D Finanzen'!D715</f>
-        <v/>
+      <c r="F17" s="6" t="n">
+        <v>6113.1</v>
       </c>
       <c r="G17" s="1" t="n"/>
       <c r="H17" s="1" t="n"/>
@@ -1004,9 +991,8 @@
           <t>Summe Umlaufvermoegen</t>
         </is>
       </c>
-      <c r="F18" s="9">
-        <f>'[D Finanzen.xlsx]D Finanzen'!D716</f>
-        <v/>
+      <c r="F18" s="9" t="n">
+        <v>6295192.72</v>
       </c>
       <c r="G18" s="1" t="n"/>
       <c r="H18" s="1" t="n"/>
@@ -1034,9 +1020,8 @@
           <t>Summe ARAP</t>
         </is>
       </c>
-      <c r="F19" s="9">
-        <f>'[D Finanzen.xlsx]D Finanzen'!D722</f>
-        <v/>
+      <c r="F19" s="9" t="n">
+        <v>9364</v>
       </c>
       <c r="G19" s="1" t="n"/>
       <c r="H19" s="1" t="n"/>
@@ -1064,9 +1049,8 @@
           <t>Summe      A K T I V A</t>
         </is>
       </c>
-      <c r="F20" s="9">
-        <f>'[D Finanzen.xlsx]D Finanzen'!D723</f>
-        <v/>
+      <c r="F20" s="9" t="n">
+        <v>6753194.72</v>
       </c>
       <c r="G20" s="1" t="n"/>
       <c r="H20" s="1" t="n"/>
@@ -1094,9 +1078,8 @@
           <t>Summe Eigenkapital</t>
         </is>
       </c>
-      <c r="F21" s="9">
-        <f>-'[D Finanzen.xlsx]D Finanzen'!D734</f>
-        <v/>
+      <c r="F21" s="9" t="n">
+        <v>3063943.93</v>
       </c>
       <c r="G21" s="1" t="n"/>
       <c r="H21" s="1" t="n"/>
@@ -1124,9 +1107,8 @@
           <t>Summe Rueckstellungen</t>
         </is>
       </c>
-      <c r="F22" s="9">
-        <f>-'[D Finanzen.xlsx]D Finanzen'!D748</f>
-        <v/>
+      <c r="F22" s="9" t="n">
+        <v>546686.02</v>
       </c>
       <c r="G22" s="1" t="n"/>
       <c r="H22" s="1" t="n"/>
@@ -1154,9 +1136,8 @@
           <t>Summe Verbindlk. L+L</t>
         </is>
       </c>
-      <c r="F23" s="6">
-        <f>-'[D Finanzen.xlsx]D Finanzen'!D755</f>
-        <v/>
+      <c r="F23" s="6" t="n">
+        <v>1403813.01</v>
       </c>
       <c r="G23" s="1" t="n"/>
       <c r="H23" s="1" t="n"/>
@@ -1184,9 +1165,8 @@
           <t>Summe Verblk. verbund.</t>
         </is>
       </c>
-      <c r="F24" s="6">
-        <f>-'[D Finanzen.xlsx]D Finanzen'!D766</f>
-        <v/>
+      <c r="F24" s="6" t="n">
+        <v>994089.85</v>
       </c>
       <c r="G24" s="1" t="n"/>
       <c r="H24" s="1" t="n"/>
@@ -1214,9 +1194,8 @@
           <t>Summe And. Sonst. Verbindlk.</t>
         </is>
       </c>
-      <c r="F25" s="6">
-        <f>-'[D Finanzen.xlsx]D Finanzen'!D789</f>
-        <v/>
+      <c r="F25" s="6" t="n">
+        <v>368065.18</v>
       </c>
       <c r="G25" s="1" t="n"/>
       <c r="H25" s="1" t="n"/>
@@ -1244,9 +1223,8 @@
           <t>Summe Sonst. Verbindlichkeiten</t>
         </is>
       </c>
-      <c r="F26" s="6">
-        <f>-'[D Finanzen.xlsx]D Finanzen'!D790</f>
-        <v/>
+      <c r="F26" s="6" t="n">
+        <v>744661.91</v>
       </c>
       <c r="G26" s="1" t="n"/>
       <c r="H26" s="1" t="n"/>
@@ -1274,9 +1252,8 @@
           <t>Summe Verbindlichkeiten</t>
         </is>
       </c>
-      <c r="F27" s="9">
-        <f>-'[D Finanzen.xlsx]D Finanzen'!D791</f>
-        <v/>
+      <c r="F27" s="9" t="n">
+        <v>3142564.77</v>
       </c>
       <c r="G27" s="1" t="n"/>
       <c r="H27" s="1" t="n"/>
@@ -1304,9 +1281,8 @@
           <t>Summe      P A S S I V A</t>
         </is>
       </c>
-      <c r="F28" s="9">
-        <f>-'[D Finanzen.xlsx]D Finanzen'!D797</f>
-        <v/>
+      <c r="F28" s="9" t="n">
+        <v>6753194.72</v>
       </c>
       <c r="G28" s="1" t="n"/>
       <c r="H28" s="1" t="n"/>
@@ -1830,9 +1806,8 @@
           <t>Anlagevermögen</t>
         </is>
       </c>
-      <c r="D72" s="11">
-        <f>SUM('[D Finanzen.xlsx]D Finanzen'!D633,'[D Finanzen.xlsx]D Finanzen'!D634,'[D Finanzen.xlsx]D Finanzen'!D635,'[D Finanzen.xlsx]D Finanzen'!D640,'[D Finanzen.xlsx]D Finanzen'!D641,'[D Finanzen.xlsx]D Finanzen'!D642,'[D Finanzen.xlsx]D Finanzen'!D643,'[D Finanzen.xlsx]D Finanzen'!D645,'[D Finanzen.xlsx]D Finanzen'!D647,'[D Finanzen.xlsx]D Finanzen'!D648,'[D Finanzen.xlsx]D Finanzen'!D649,'[D Finanzen.xlsx]D Finanzen'!D650,'[D Finanzen.xlsx]D Finanzen'!D651,'[D Finanzen.xlsx]D Finanzen'!D652,'[D Finanzen.xlsx]D Finanzen'!D653)</f>
-        <v/>
+      <c r="D72" s="11" t="n">
+        <v>448638</v>
       </c>
     </row>
     <row r="73">
@@ -1841,9 +1816,8 @@
           <t>Umlaufvermögen inkl. ARAP</t>
         </is>
       </c>
-      <c r="D73" s="11">
-        <f>SUM('[D Finanzen.xlsx]D Finanzen'!D661,'[D Finanzen.xlsx]D Finanzen'!D663,'[D Finanzen.xlsx]D Finanzen'!D665,'[D Finanzen.xlsx]D Finanzen'!D670,'[D Finanzen.xlsx]D Finanzen'!D671,'[D Finanzen.xlsx]D Finanzen'!D673,'[D Finanzen.xlsx]D Finanzen'!D675,'[D Finanzen.xlsx]D Finanzen'!D676,'[D Finanzen.xlsx]D Finanzen'!D680,'[D Finanzen.xlsx]D Finanzen'!D681,'[D Finanzen.xlsx]D Finanzen'!D682,'[D Finanzen.xlsx]D Finanzen'!D687,'[D Finanzen.xlsx]D Finanzen'!D688,'[D Finanzen.xlsx]D Finanzen'!D689,'[D Finanzen.xlsx]D Finanzen'!D690,'[D Finanzen.xlsx]D Finanzen'!D691,'[D Finanzen.xlsx]D Finanzen'!D692,'[D Finanzen.xlsx]D Finanzen'!D695,'[D Finanzen.xlsx]D Finanzen'!D696,'[D Finanzen.xlsx]D Finanzen'!D697,'[D Finanzen.xlsx]D Finanzen'!D698,'[D Finanzen.xlsx]D Finanzen'!D699,'[D Finanzen.xlsx]D Finanzen'!D700,'[D Finanzen.xlsx]D Finanzen'!D701,'[D Finanzen.xlsx]D Finanzen'!D702,'[D Finanzen.xlsx]D Finanzen'!D704,'[D Finanzen.xlsx]D Finanzen'!D705,'[D Finanzen.xlsx]D Finanzen'!D711,'[D Finanzen.xlsx]D Finanzen'!D712,'[D Finanzen.xlsx]D Finanzen'!D713,'[D Finanzen.xlsx]D Finanzen'!D714)+SUM('[D Finanzen.xlsx]D Finanzen'!D719,'[D Finanzen.xlsx]D Finanzen'!D720,'[D Finanzen.xlsx]D Finanzen'!D721)</f>
-        <v/>
+      <c r="D73" s="11" t="n">
+        <v>6304556.719999997</v>
       </c>
     </row>
     <row r="74">
@@ -1852,9 +1826,8 @@
           <t>Forderungen</t>
         </is>
       </c>
-      <c r="D74" s="11">
-        <f>SUM('[D Finanzen.xlsx]D Finanzen'!D670,'[D Finanzen.xlsx]D Finanzen'!D671,'[D Finanzen.xlsx]D Finanzen'!D673,'[D Finanzen.xlsx]D Finanzen'!D675,'[D Finanzen.xlsx]D Finanzen'!D676,'[D Finanzen.xlsx]D Finanzen'!D680,'[D Finanzen.xlsx]D Finanzen'!D681,'[D Finanzen.xlsx]D Finanzen'!D682)</f>
-        <v/>
+      <c r="D74" s="11" t="n">
+        <v>1685211.35</v>
       </c>
     </row>
     <row r="75">
@@ -1863,9 +1836,8 @@
           <t>Liquide Mittel</t>
         </is>
       </c>
-      <c r="D75" s="11">
-        <f>SUM('[D Finanzen.xlsx]D Finanzen'!D711,'[D Finanzen.xlsx]D Finanzen'!D712,'[D Finanzen.xlsx]D Finanzen'!D713,'[D Finanzen.xlsx]D Finanzen'!D714)</f>
-        <v/>
+      <c r="D75" s="11" t="n">
+        <v>6113.1</v>
       </c>
     </row>
     <row r="76">
@@ -1874,9 +1846,8 @@
           <t>Vorräte netto</t>
         </is>
       </c>
-      <c r="D76" s="11">
-        <f>SUM('[D Finanzen.xlsx]D Finanzen'!D661,'[D Finanzen.xlsx]D Finanzen'!D663,'[D Finanzen.xlsx]D Finanzen'!D665)</f>
-        <v/>
+      <c r="D76" s="11" t="n">
+        <v>2332501.169999998</v>
       </c>
     </row>
     <row r="77">
@@ -1885,9 +1856,8 @@
           <t>Eigenkapital</t>
         </is>
       </c>
-      <c r="D77" s="11">
-        <f>-SUM('[D Finanzen.xlsx]D Finanzen'!D727,'[D Finanzen.xlsx]D Finanzen'!D729,'[D Finanzen.xlsx]D Finanzen'!D732,'[D Finanzen.xlsx]D Finanzen'!D733)</f>
-        <v/>
+      <c r="D77" s="11" t="n">
+        <v>3063943.93</v>
       </c>
     </row>
     <row r="78">
@@ -1896,9 +1866,8 @@
           <t>Fremdkapital</t>
         </is>
       </c>
-      <c r="D78" s="11">
-        <f>-SUM('[D Finanzen.xlsx]D Finanzen'!D736,'[D Finanzen.xlsx]D Finanzen'!D738,'[D Finanzen.xlsx]D Finanzen'!D739,'[D Finanzen.xlsx]D Finanzen'!D740,'[D Finanzen.xlsx]D Finanzen'!D741,'[D Finanzen.xlsx]D Finanzen'!D742,'[D Finanzen.xlsx]D Finanzen'!D743,'[D Finanzen.xlsx]D Finanzen'!D745,'[D Finanzen.xlsx]D Finanzen'!D746,'[D Finanzen.xlsx]D Finanzen'!D747)+-SUM('[D Finanzen.xlsx]D Finanzen'!D752,'[D Finanzen.xlsx]D Finanzen'!D753,'[D Finanzen.xlsx]D Finanzen'!D754,'[D Finanzen.xlsx]D Finanzen'!D758,'[D Finanzen.xlsx]D Finanzen'!D759,'[D Finanzen.xlsx]D Finanzen'!D761,'[D Finanzen.xlsx]D Finanzen'!D763,'[D Finanzen.xlsx]D Finanzen'!D764,'[D Finanzen.xlsx]D Finanzen'!D765,'[D Finanzen.xlsx]D Finanzen'!D770,'[D Finanzen.xlsx]D Finanzen'!D771,'[D Finanzen.xlsx]D Finanzen'!D772,'[D Finanzen.xlsx]D Finanzen'!D773,'[D Finanzen.xlsx]D Finanzen'!D774,'[D Finanzen.xlsx]D Finanzen'!D775,'[D Finanzen.xlsx]D Finanzen'!D776,'[D Finanzen.xlsx]D Finanzen'!D777,'[D Finanzen.xlsx]D Finanzen'!D778,'[D Finanzen.xlsx]D Finanzen'!D781,'[D Finanzen.xlsx]D Finanzen'!D783,'[D Finanzen.xlsx]D Finanzen'!D784,'[D Finanzen.xlsx]D Finanzen'!D785,'[D Finanzen.xlsx]D Finanzen'!D786,'[D Finanzen.xlsx]D Finanzen'!D787,'[D Finanzen.xlsx]D Finanzen'!D788)+-SUM('[D Finanzen.xlsx]D Finanzen'!D793,'[D Finanzen.xlsx]D Finanzen'!D794,'[D Finanzen.xlsx]D Finanzen'!D795,'[D Finanzen.xlsx]D Finanzen'!D796)</f>
-        <v/>
+      <c r="D78" s="11" t="n">
+        <v>3689250.79</v>
       </c>
     </row>
     <row r="79">
@@ -1907,9 +1876,8 @@
           <t>Kurzfristiges FK lt. Original</t>
         </is>
       </c>
-      <c r="D79" s="11">
-        <f>D78</f>
-        <v/>
+      <c r="D79" s="11" t="n">
+        <v>3689250.79</v>
       </c>
     </row>
     <row r="80">
@@ -1918,9 +1886,8 @@
           <t>Langfristiges FK lt. Original</t>
         </is>
       </c>
-      <c r="D80" s="11">
-        <f>0</f>
-        <v/>
+      <c r="D80" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -1929,9 +1896,8 @@
           <t>Verbindlichkeiten L+L</t>
         </is>
       </c>
-      <c r="D81" s="11">
-        <f>-SUM('[D Finanzen.xlsx]D Finanzen'!D752,'[D Finanzen.xlsx]D Finanzen'!D753,'[D Finanzen.xlsx]D Finanzen'!D754)</f>
-        <v/>
+      <c r="D81" s="11" t="n">
+        <v>1403813.01</v>
       </c>
     </row>
     <row r="82">
@@ -1940,9 +1906,8 @@
           <t>Rückstellungen</t>
         </is>
       </c>
-      <c r="D82" s="11">
-        <f>-SUM('[D Finanzen.xlsx]D Finanzen'!D736,'[D Finanzen.xlsx]D Finanzen'!D738,'[D Finanzen.xlsx]D Finanzen'!D739,'[D Finanzen.xlsx]D Finanzen'!D740,'[D Finanzen.xlsx]D Finanzen'!D741,'[D Finanzen.xlsx]D Finanzen'!D742,'[D Finanzen.xlsx]D Finanzen'!D743,'[D Finanzen.xlsx]D Finanzen'!D745,'[D Finanzen.xlsx]D Finanzen'!D746,'[D Finanzen.xlsx]D Finanzen'!D747)</f>
-        <v/>
+      <c r="D82" s="11" t="n">
+        <v>546686.02</v>
       </c>
     </row>
     <row r="83">
@@ -1951,9 +1916,8 @@
           <t>Bilanzsumme</t>
         </is>
       </c>
-      <c r="D83" s="11">
-        <f>SUM('[D Finanzen.xlsx]D Finanzen'!D633,'[D Finanzen.xlsx]D Finanzen'!D634,'[D Finanzen.xlsx]D Finanzen'!D635,'[D Finanzen.xlsx]D Finanzen'!D640,'[D Finanzen.xlsx]D Finanzen'!D641,'[D Finanzen.xlsx]D Finanzen'!D642,'[D Finanzen.xlsx]D Finanzen'!D643,'[D Finanzen.xlsx]D Finanzen'!D645,'[D Finanzen.xlsx]D Finanzen'!D647,'[D Finanzen.xlsx]D Finanzen'!D648,'[D Finanzen.xlsx]D Finanzen'!D649,'[D Finanzen.xlsx]D Finanzen'!D650,'[D Finanzen.xlsx]D Finanzen'!D651,'[D Finanzen.xlsx]D Finanzen'!D652,'[D Finanzen.xlsx]D Finanzen'!D653,'[D Finanzen.xlsx]D Finanzen'!D661,'[D Finanzen.xlsx]D Finanzen'!D663,'[D Finanzen.xlsx]D Finanzen'!D665,'[D Finanzen.xlsx]D Finanzen'!D670,'[D Finanzen.xlsx]D Finanzen'!D671,'[D Finanzen.xlsx]D Finanzen'!D673,'[D Finanzen.xlsx]D Finanzen'!D675,'[D Finanzen.xlsx]D Finanzen'!D676,'[D Finanzen.xlsx]D Finanzen'!D680,'[D Finanzen.xlsx]D Finanzen'!D681,'[D Finanzen.xlsx]D Finanzen'!D682,'[D Finanzen.xlsx]D Finanzen'!D687,'[D Finanzen.xlsx]D Finanzen'!D688,'[D Finanzen.xlsx]D Finanzen'!D689,'[D Finanzen.xlsx]D Finanzen'!D690,'[D Finanzen.xlsx]D Finanzen'!D691,'[D Finanzen.xlsx]D Finanzen'!D692,'[D Finanzen.xlsx]D Finanzen'!D695,'[D Finanzen.xlsx]D Finanzen'!D696,'[D Finanzen.xlsx]D Finanzen'!D697,'[D Finanzen.xlsx]D Finanzen'!D698,'[D Finanzen.xlsx]D Finanzen'!D699,'[D Finanzen.xlsx]D Finanzen'!D700,'[D Finanzen.xlsx]D Finanzen'!D701,'[D Finanzen.xlsx]D Finanzen'!D702,'[D Finanzen.xlsx]D Finanzen'!D704,'[D Finanzen.xlsx]D Finanzen'!D705,'[D Finanzen.xlsx]D Finanzen'!D711,'[D Finanzen.xlsx]D Finanzen'!D712,'[D Finanzen.xlsx]D Finanzen'!D713,'[D Finanzen.xlsx]D Finanzen'!D714,'[D Finanzen.xlsx]D Finanzen'!D719,'[D Finanzen.xlsx]D Finanzen'!D720,'[D Finanzen.xlsx]D Finanzen'!D721)</f>
-        <v/>
+      <c r="D83" s="11" t="n">
+        <v>6753194.719999998</v>
       </c>
     </row>
     <row r="84"/>
@@ -1966,6 +1930,8 @@
       </c>
     </row>
     <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
     <row r="90">
       <c r="C90" t="inlineStr">
         <is>
